--- a/cases/Case_14bus_v2/pf_info_Case_14bus_v2.xlsx
+++ b/cases/Case_14bus_v2/pf_info_Case_14bus_v2.xlsx
@@ -435,10 +435,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.193147541346318</v>
+        <v>1.225518223298555</v>
       </c>
       <c r="C2">
-        <v>-0.2555810298046648</v>
+        <v>-0.2606062912806886</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -447,16 +447,16 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.193147541346318</v>
+        <v>1.225518223298555</v>
       </c>
       <c r="G2">
-        <v>-0.2555810298046648</v>
+        <v>-0.2606062912806886</v>
       </c>
       <c r="H2">
         <v>1.03</v>
       </c>
       <c r="I2">
-        <v>1.579513746415983E-16</v>
+        <v>1.670418904637509E-16</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -464,10 +464,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.1829998806858328</v>
+        <v>0.1829998771464987</v>
       </c>
       <c r="C3">
-        <v>0.3366435096112541</v>
+        <v>0.3450450100777331</v>
       </c>
       <c r="D3">
         <v>0.217</v>
@@ -476,16 +476,16 @@
         <v>0.127</v>
       </c>
       <c r="F3">
-        <v>0.3999998806858328</v>
+        <v>0.3999998771464987</v>
       </c>
       <c r="G3">
-        <v>0.4636435096112541</v>
+        <v>0.4720450100777331</v>
       </c>
       <c r="H3">
         <v>1.03</v>
       </c>
       <c r="I3">
-        <v>-0.04525370883924262</v>
+        <v>-0.04651415196203403</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -493,10 +493,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-0.1000000034096129</v>
+        <v>-0.1000000034486059</v>
       </c>
       <c r="C4">
-        <v>-0.05771877492493704</v>
+        <v>-0.055180872682004</v>
       </c>
       <c r="D4">
         <v>0.5</v>
@@ -505,16 +505,16 @@
         <v>0.25</v>
       </c>
       <c r="F4">
-        <v>0.3999999965903871</v>
+        <v>0.3999999965513941</v>
       </c>
       <c r="G4">
-        <v>0.192281225075063</v>
+        <v>0.194819127317996</v>
       </c>
       <c r="H4">
         <v>1.01</v>
       </c>
       <c r="I4">
-        <v>-0.08496263997583167</v>
+        <v>-0.08703660390633892</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -522,10 +522,10 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-0.4780000695748242</v>
+        <v>-0.4780000707158899</v>
       </c>
       <c r="C5">
-        <v>-0.1000000685037656</v>
+        <v>-0.1000000684005</v>
       </c>
       <c r="D5">
         <v>0.478</v>
@@ -534,16 +534,16 @@
         <v>0.1</v>
       </c>
       <c r="F5">
-        <v>-6.957482417968563E-08</v>
+        <v>-7.071588992157984E-08</v>
       </c>
       <c r="G5">
-        <v>-6.850376563227734E-08</v>
+        <v>-6.840050001399867E-08</v>
       </c>
       <c r="H5">
-        <v>0.9993857339846809</v>
+        <v>0.9988917002221633</v>
       </c>
       <c r="I5">
-        <v>-0.104083398095561</v>
+        <v>-0.1067518617762736</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -551,10 +551,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-0.07599998053385121</v>
+        <v>-0.07599998012731524</v>
       </c>
       <c r="C6">
-        <v>-0.01599995207523364</v>
+        <v>-0.01599995202966387</v>
       </c>
       <c r="D6">
         <v>0.076</v>
@@ -563,16 +563,16 @@
         <v>0.016</v>
       </c>
       <c r="F6">
-        <v>1.946614879011488E-08</v>
+        <v>1.987268476166815E-08</v>
       </c>
       <c r="G6">
-        <v>4.792476636372722E-08</v>
+        <v>4.797033613390678E-08</v>
       </c>
       <c r="H6">
-        <v>1.006113812417038</v>
+        <v>1.005594239924474</v>
       </c>
       <c r="I6">
-        <v>-0.09698166615960305</v>
+        <v>-0.09952080186882445</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -580,10 +580,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.1500000112623767</v>
+        <v>0.1500000113766555</v>
       </c>
       <c r="C7">
-        <v>0.7424795266860169</v>
+        <v>0.7484348020160567</v>
       </c>
       <c r="D7">
         <v>0.15</v>
@@ -592,16 +592,16 @@
         <v>0.075</v>
       </c>
       <c r="F7">
-        <v>0.3000000112623767</v>
+        <v>0.3000000113766556</v>
       </c>
       <c r="G7">
-        <v>0.8174795266860169</v>
+        <v>0.8234348020160567</v>
       </c>
       <c r="H7">
         <v>1.03</v>
       </c>
       <c r="I7">
-        <v>-0.2151738720070119</v>
+        <v>-0.2217321730629859</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -609,10 +609,10 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>7.950072267171038E-09</v>
+        <v>8.329833711684387E-09</v>
       </c>
       <c r="C8">
-        <v>2.304383350804073E-08</v>
+        <v>2.345160510230926E-08</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -621,16 +621,16 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>7.950072267171038E-09</v>
+        <v>8.329833711684387E-09</v>
       </c>
       <c r="G8">
-        <v>2.304383350804073E-08</v>
+        <v>2.345160510230926E-08</v>
       </c>
       <c r="H8">
-        <v>0.9942537894021076</v>
+        <v>0.9939391233147048</v>
       </c>
       <c r="I8">
-        <v>-0.1214317925431795</v>
+        <v>-0.126039810609252</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -638,10 +638,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.3500000074048571</v>
+        <v>0.3500000073002139</v>
       </c>
       <c r="C9">
-        <v>0.2195634749746596</v>
+        <v>0.2214067630660983</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -650,16 +650,16 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0.3500000074048571</v>
+        <v>0.3500000073002139</v>
       </c>
       <c r="G9">
-        <v>0.2195634749746596</v>
+        <v>0.2214067630660983</v>
       </c>
       <c r="H9">
         <v>1.03</v>
       </c>
       <c r="I9">
-        <v>-0.06119263196891782</v>
+        <v>-0.06578155613395506</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -667,10 +667,10 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-0.2950000128134511</v>
+        <v>-0.2950000117761942</v>
       </c>
       <c r="C10">
-        <v>-0.166000056244946</v>
+        <v>-0.1660000563026931</v>
       </c>
       <c r="D10">
         <v>0.295</v>
@@ -679,16 +679,16 @@
         <v>0.166</v>
       </c>
       <c r="F10">
-        <v>-1.281345113346433E-08</v>
+        <v>-1.177619418646358E-08</v>
       </c>
       <c r="G10">
-        <v>-5.624494595068974E-08</v>
+        <v>-5.630269309109259E-08</v>
       </c>
       <c r="H10">
-        <v>0.9716542999096324</v>
+        <v>0.9713084496386745</v>
       </c>
       <c r="I10">
-        <v>-0.1706938062007487</v>
+        <v>-0.1763777964017369</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -696,10 +696,10 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.110000008055732</v>
+        <v>0.1100000069618283</v>
       </c>
       <c r="C11">
-        <v>-0.05799999764902886</v>
+        <v>-0.05799999817030699</v>
       </c>
       <c r="D11">
         <v>0.09</v>
@@ -708,16 +708,16 @@
         <v>0.058</v>
       </c>
       <c r="F11">
-        <v>0.200000008055732</v>
+        <v>0.2000000069618283</v>
       </c>
       <c r="G11">
-        <v>2.350971146924952E-09</v>
+        <v>1.82969301515401E-09</v>
       </c>
       <c r="H11">
-        <v>0.9750211180791037</v>
+        <v>0.9742492550922061</v>
       </c>
       <c r="I11">
-        <v>-0.1706947015053131</v>
+        <v>-0.1776002318955821</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -725,10 +725,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>-0.1100000047208138</v>
+        <v>-0.1400000065698666</v>
       </c>
       <c r="C12">
-        <v>-0.1180000096327412</v>
+        <v>-0.1180000103238026</v>
       </c>
       <c r="D12">
         <v>0.135</v>
@@ -737,16 +737,16 @@
         <v>0.118</v>
       </c>
       <c r="F12">
-        <v>0.02499999527918617</v>
+        <v>-0.005000006569866544</v>
       </c>
       <c r="G12">
-        <v>-9.632741160281455E-09</v>
+        <v>-1.032380259058385E-08</v>
       </c>
       <c r="H12">
-        <v>0.9853376637764527</v>
+        <v>0.983543646155976</v>
       </c>
       <c r="I12">
-        <v>-0.1979901473440626</v>
+        <v>-0.2077122419649518</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -754,10 +754,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>-0.03600000044553209</v>
+        <v>-0.03600000044204688</v>
       </c>
       <c r="C13">
-        <v>-0.01600000340239882</v>
+        <v>-0.01600000340044971</v>
       </c>
       <c r="D13">
         <v>0.061</v>
@@ -766,16 +766,16 @@
         <v>0.016</v>
       </c>
       <c r="F13">
-        <v>0.02499999955446791</v>
+        <v>0.02499999955795312</v>
       </c>
       <c r="G13">
-        <v>-3.402398821017449E-09</v>
+        <v>-3.400449713475417E-09</v>
       </c>
       <c r="H13">
-        <v>0.9946095075366331</v>
+        <v>0.9945738702802914</v>
       </c>
       <c r="I13">
-        <v>-0.2437348388486146</v>
+        <v>-0.250246908317458</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -783,10 +783,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>-0.5350000387086744</v>
+        <v>-0.5350000386686247</v>
       </c>
       <c r="C14">
-        <v>-0.2000000366319248</v>
+        <v>-0.2000000366640946</v>
       </c>
       <c r="D14">
         <v>0.635</v>
@@ -795,16 +795,16 @@
         <v>0.2</v>
       </c>
       <c r="F14">
-        <v>0.0999999612913256</v>
+        <v>0.09999996133137534</v>
       </c>
       <c r="G14">
-        <v>-3.663192477132426E-08</v>
+        <v>-3.66640945936858E-08</v>
       </c>
       <c r="H14">
-        <v>0.9602296287510631</v>
+        <v>0.9601766181227075</v>
       </c>
       <c r="I14">
-        <v>-0.255229436265854</v>
+        <v>-0.2616785350407841</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -812,10 +812,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>-0.2709409785544681</v>
+        <v>-0.2709409785642332</v>
       </c>
       <c r="C15">
-        <v>-0.2000000119690819</v>
+        <v>-0.2000000119641472</v>
       </c>
       <c r="D15">
         <v>0.4</v>
@@ -824,16 +824,16 @@
         <v>0.2</v>
       </c>
       <c r="F15">
-        <v>0.1290590214455319</v>
+        <v>0.1290590214357669</v>
       </c>
       <c r="G15">
-        <v>-1.19690818922713E-08</v>
+        <v>-1.196414717297145E-08</v>
       </c>
       <c r="H15">
-        <v>0.9106126696140026</v>
+        <v>0.910366817412159</v>
       </c>
       <c r="I15">
-        <v>-0.2375764512905657</v>
+        <v>-0.2436115958364653</v>
       </c>
     </row>
   </sheetData>
